--- a/artfynd/A 45201-2024 artfynd.xlsx
+++ b/artfynd/A 45201-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1175,147 +1175,6 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>109519333</v>
-      </c>
-      <c r="B6" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>967</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Varglav</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Letharia vulpina</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Storfjäten, Storfjäten, Idre, Hjd</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>400755.8887308697</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6873395.472564099</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Idre</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2023-05-25</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2023-05-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Brandpåverkad tallskog. Fjällnära skog.</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45201-2024 artfynd.xlsx
+++ b/artfynd/A 45201-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109509186</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109512679</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109519333</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1169,6 +1189,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109520266</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1295,6 +1320,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109522771</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1436,6 +1466,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109522792</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1555,8 +1590,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109510187</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>